--- a/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_non_biogenic_waste_ccs.xlsx
+++ b/nodes_source_analyses/energy/energy/energy_production_methanol_synthesis_non_biogenic_waste_ccs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyradehaan/github/etdataset/nodes_source_analyses/energy/energy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robin/Desktop/Quintel/etdataset/nodes_source_analyses/energy/energy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729AAA16-A91B-FD4A-925B-D9D293430FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20DDFB9-D064-4B48-86B9-DFAC1D5D7538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" tabRatio="762" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="700" windowWidth="28800" windowHeight="15820" tabRatio="762" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="225">
   <si>
     <t>Source</t>
   </si>
@@ -877,6 +877,12 @@
   </si>
   <si>
     <t>Methanol</t>
+  </si>
+  <si>
+    <t>Is the actual CO2 capture rate</t>
+  </si>
+  <si>
+    <t>Taken from energy_hydrogen_biomass_gasification_ccs</t>
   </si>
 </sst>
 </file>
@@ -2596,12 +2602,17 @@
     <xf numFmtId="9" fontId="53" fillId="14" borderId="22" xfId="499" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="60" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="2" xfId="498" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2629,12 +2640,7 @@
     <xf numFmtId="0" fontId="35" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="2" xfId="498" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="60" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="501">
     <cellStyle name="Comma" xfId="496" builtinId="3"/>
@@ -3524,6 +3530,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -3637,6 +3646,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Title"/>
       <sheetName val="Description"/>
@@ -4021,12 +4033,12 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" style="18" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="18"/>
+    <col min="1" max="1" width="3.5" style="26" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="18" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="18" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="24" customFormat="1">
@@ -4222,44 +4234,44 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A2:J44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="29" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="29" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="29" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="29" customWidth="1"/>
-    <col min="7" max="7" width="49.42578125" style="29" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" style="29" customWidth="1"/>
-    <col min="9" max="9" width="42.42578125" style="29" customWidth="1"/>
-    <col min="10" max="10" width="5.42578125" style="29" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="29"/>
+    <col min="1" max="2" width="3.5" style="29" customWidth="1"/>
+    <col min="3" max="3" width="51.5" style="29" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="4.5" style="29" customWidth="1"/>
+    <col min="7" max="7" width="49.5" style="29" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="29" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="29" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="29"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
+      <c r="C2" s="252"/>
+      <c r="D2" s="252"/>
+      <c r="E2" s="253"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="B3" s="253"/>
-      <c r="C3" s="254"/>
-      <c r="D3" s="254"/>
-      <c r="E3" s="255"/>
+      <c r="B3" s="254"/>
+      <c r="C3" s="255"/>
+      <c r="D3" s="255"/>
+      <c r="E3" s="256"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="253"/>
-      <c r="C4" s="254"/>
-      <c r="D4" s="254"/>
-      <c r="E4" s="255"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="256"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="256"/>
-      <c r="C5" s="257"/>
-      <c r="D5" s="257"/>
-      <c r="E5" s="258"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="258"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="259"/>
     </row>
     <row r="7" spans="1:10" ht="17" thickBot="1"/>
     <row r="8" spans="1:10">
@@ -4328,7 +4340,7 @@
     </row>
     <row r="13" spans="1:10" s="110" customFormat="1" ht="16" customHeight="1" thickBot="1">
       <c r="B13" s="111"/>
-      <c r="C13" s="249" t="s">
+      <c r="C13" s="248" t="s">
         <v>216</v>
       </c>
       <c r="D13" s="106"/>
@@ -4346,7 +4358,7 @@
     <row r="14" spans="1:10" ht="17" thickBot="1">
       <c r="A14" s="72"/>
       <c r="B14" s="73"/>
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="247" t="s">
         <v>215</v>
       </c>
       <c r="D14" s="19" t="s">
@@ -4698,13 +4710,13 @@
       </c>
       <c r="E33" s="75">
         <f>Notes!D97</f>
-        <v>0.53939300000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F33" s="71"/>
       <c r="G33" s="71"/>
       <c r="H33" s="71"/>
       <c r="I33" s="102" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="J33" s="74"/>
     </row>
@@ -4835,24 +4847,24 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A2:P27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="35" customWidth="1"/>
     <col min="2" max="2" width="3" style="35" customWidth="1"/>
     <col min="3" max="3" width="61" style="35" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="35" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="35" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="35" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="35" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="35" customWidth="1"/>
     <col min="7" max="7" width="3" style="35" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="35" customWidth="1"/>
-    <col min="9" max="9" width="2.42578125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="35" customWidth="1"/>
-    <col min="11" max="12" width="2.42578125" style="35" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" style="35" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="2.5" style="35" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="35" customWidth="1"/>
+    <col min="11" max="12" width="2.5" style="35" customWidth="1"/>
+    <col min="13" max="13" width="23.5" style="35" customWidth="1"/>
     <col min="14" max="14" width="11" style="35" customWidth="1"/>
-    <col min="15" max="15" width="2.42578125" style="35" customWidth="1"/>
-    <col min="16" max="16" width="22.42578125" style="35" customWidth="1"/>
-    <col min="17" max="16384" width="10.85546875" style="35"/>
+    <col min="15" max="15" width="2.5" style="35" customWidth="1"/>
+    <col min="16" max="16" width="22.5" style="35" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="35"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="17" thickBot="1"/>
@@ -5398,19 +5410,19 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="44" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" style="44" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" style="44" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" style="44" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" style="44" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="44" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="44" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="44" customWidth="1"/>
+    <col min="3" max="3" width="24.5" style="44" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" style="44" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" style="44" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="44" customWidth="1"/>
     <col min="7" max="7" width="78" style="44" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="48" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="98.42578125" style="44" customWidth="1"/>
-    <col min="11" max="16384" width="33.140625" style="44"/>
+    <col min="8" max="8" width="12.5" style="48" customWidth="1"/>
+    <col min="9" max="9" width="31.5" style="48" customWidth="1"/>
+    <col min="10" max="10" width="98.5" style="44" customWidth="1"/>
+    <col min="11" max="16384" width="33.1640625" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17" thickBot="1"/>
@@ -5587,20 +5599,20 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Z113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="51" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="51" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="51" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" style="51" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="51" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="10.85546875" style="51"/>
-    <col min="10" max="10" width="23.42578125" style="51" customWidth="1"/>
-    <col min="11" max="13" width="10.85546875" style="51"/>
-    <col min="14" max="14" width="28.140625" style="51" customWidth="1"/>
-    <col min="15" max="15" width="23.42578125" style="51" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" style="51" customWidth="1"/>
-    <col min="17" max="16384" width="10.85546875" style="51"/>
+    <col min="1" max="2" width="3.5" style="51" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="51" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="51" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="51" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" style="51" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="10.83203125" style="51"/>
+    <col min="10" max="10" width="23.5" style="51" customWidth="1"/>
+    <col min="11" max="13" width="10.83203125" style="51"/>
+    <col min="14" max="14" width="28.1640625" style="51" customWidth="1"/>
+    <col min="15" max="15" width="23.5" style="51" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" style="51" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17" thickBot="1"/>
@@ -5902,19 +5914,19 @@
         <v>135</v>
       </c>
       <c r="O25" s="132"/>
-      <c r="P25" s="259" t="s">
+      <c r="P25" s="249" t="s">
         <v>136</v>
       </c>
-      <c r="Q25" s="260"/>
-      <c r="R25" s="260"/>
-      <c r="S25" s="260"/>
-      <c r="T25" s="260"/>
-      <c r="U25" s="260"/>
-      <c r="V25" s="260"/>
-      <c r="W25" s="260"/>
-      <c r="X25" s="260"/>
-      <c r="Y25" s="260"/>
-      <c r="Z25" s="260"/>
+      <c r="Q25" s="250"/>
+      <c r="R25" s="250"/>
+      <c r="S25" s="250"/>
+      <c r="T25" s="250"/>
+      <c r="U25" s="250"/>
+      <c r="V25" s="250"/>
+      <c r="W25" s="250"/>
+      <c r="X25" s="250"/>
+      <c r="Y25" s="250"/>
+      <c r="Z25" s="250"/>
     </row>
     <row r="26" spans="1:26" ht="17" customHeight="1">
       <c r="A26" s="55"/>
@@ -7429,7 +7441,7 @@
     </row>
     <row r="75" spans="1:25">
       <c r="C75" s="199"/>
-      <c r="F75" s="247" t="s">
+      <c r="F75" s="246" t="s">
         <v>213</v>
       </c>
       <c r="W75" s="164"/>
@@ -7437,7 +7449,7 @@
       <c r="Y75" s="163"/>
     </row>
     <row r="76" spans="1:25">
-      <c r="F76" s="247" t="s">
+      <c r="F76" s="246" t="s">
         <v>214</v>
       </c>
       <c r="W76" s="164"/>
@@ -7794,15 +7806,14 @@
       <c r="C97" s="244" t="s">
         <v>187</v>
       </c>
-      <c r="D97" s="246">
-        <f>ROUND(G86/D83,6)</f>
-        <v>0.53939300000000001</v>
+      <c r="D97" s="203">
+        <v>0.9</v>
       </c>
       <c r="E97" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="F97" s="244" t="s">
-        <v>210</v>
+      <c r="F97" s="260" t="s">
+        <v>223</v>
       </c>
       <c r="G97" s="244"/>
       <c r="H97" s="244"/>
@@ -7814,7 +7825,7 @@
       <c r="Y97" s="163"/>
     </row>
     <row r="98" spans="3:25">
-      <c r="C98" s="248" t="s">
+      <c r="C98" s="247" t="s">
         <v>219</v>
       </c>
       <c r="D98" s="245">
